--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -29,7 +29,7 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>VAT: {{organization.vatin}}</t>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
   </si>
   <si>
     <t>{{organization.email}} | {{organization.phone}}</t>
@@ -62,7 +62,7 @@
     <t>{{client.postalCode}} {{client.city}}</t>
   </si>
   <si>
-    <t>VAT: {{client.vatin}}</t>
+    <t>Matricule fiscal: {{client.vatin}}</t>
   </si>
   <si>
     <t>Product</t>

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -7,18 +7,21 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Invoice" sheetId="1" r:id="rId1"/>
+    <sheet name="Facture" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Invoice'!$1:$13</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Facture'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+  <si>
+    <t>{{organization.logo}}</t>
+  </si>
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -29,298 +32,376 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{organization.email}} | {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>INVOICE</t>
-  </si>
-  <si>
-    <t>Invoice number: {{invoice.number}}</t>
-  </si>
-  <si>
-    <t>Date: {{invoice.date}}</t>
-  </si>
-  <si>
-    <t>Due date: {{invoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Buyer reference: {{invoice.buyerReference}}</t>
-  </si>
-  <si>
-    <t>Bill To</t>
+    <t>Tél : {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>MF : {{organization.vatin}}</t>
   </si>
   <si>
     <t>{{client.name}}</t>
   </si>
   <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
+    <t>{{client.address}}</t>
   </si>
   <si>
     <t>{{client.postalCode}} {{client.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Product</t>
+    <t>Tel: {{client.phone}}</t>
+  </si>
+  <si>
+    <t>CIN: {{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Facture N°: {{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Date : {{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>P.U HT</t>
+  </si>
+  <si>
+    <t>TOTAL HT</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Taux TVA %</t>
+  </si>
+  <si>
+    <t>Base TVA</t>
+  </si>
+  <si>
+    <t>Montant TVA</t>
+  </si>
+  <si>
+    <t>{{taxLines.rate}}</t>
+  </si>
+  <si>
+    <t>{{taxLines.base}}</t>
+  </si>
+  <si>
+    <t>{{taxLines.amount}}</t>
+  </si>
+  <si>
+    <t>{{#taxLines}}</t>
+  </si>
+  <si>
+    <t>Total Brut HTVA</t>
+  </si>
+  <si>
+    <t>{{invoice.subTotal}}</t>
+  </si>
+  <si>
+    <t>Remise</t>
+  </si>
+  <si>
+    <t>{{invoice.discountAmount}}</t>
+  </si>
+  <si>
+    <t>Total Net HTVA</t>
+  </si>
+  <si>
+    <t>{{invoice.netTaxable}}</t>
+  </si>
+  <si>
+    <t>Total TVA</t>
+  </si>
+  <si>
+    <t>{{invoice.taxTotal}}</t>
+  </si>
+  <si>
+    <t>D.Timbre</t>
+  </si>
+  <si>
+    <t>{{invoice.fiscalStampAmount}}</t>
+  </si>
+  <si>
+    <t>Total TTC</t>
+  </si>
+  <si>
+    <t>{{invoice.total}}</t>
+  </si>
+  <si>
+    <t>{{invoice.amountInWords}}</t>
+  </si>
+  <si>
+    <t>Cachet et Signature</t>
+  </si>
+  <si>
+    <t>IBAN : {{organization.iban}}</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there (blank if the org has none)</t>
+  </si>
+  <si>
+    <t>{{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Invoice number</t>
+  </si>
+  <si>
+    <t>{{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
+  </si>
+  <si>
+    <t>{{invoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Payment due date</t>
+  </si>
+  <si>
+    <t>{{invoice.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{invoice.buyerReference}}</t>
+  </si>
+  <si>
+    <t>Buyer reference (e.g. a Leitweg-ID)</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT / MF number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT / MF number</t>
+  </si>
+  <si>
+    <t>{{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Customer national ID / CIN number</t>
+  </si>
+  <si>
+    <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>{{client.email}}</t>
+  </si>
+  <si>
+    <t>Customer email</t>
+  </si>
+  <si>
+    <t>{{client.phone}}</t>
+  </si>
+  <si>
+    <t>Customer phone</t>
+  </si>
+  <si>
+    <t>{{client.phone2}}</t>
+  </si>
+  <si>
+    <t>Customer phone 2</t>
+  </si>
+  <si>
+    <t>{{client.phone3}}</t>
+  </si>
+  <si>
+    <t>Customer phone 3</t>
+  </si>
+  <si>
+    <t>{{client.street}}</t>
+  </si>
+  <si>
+    <t>Customer street</t>
+  </si>
+  <si>
+    <t>{{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Customer house number</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}}</t>
+  </si>
+  <si>
+    <t>Customer postal code</t>
+  </si>
+  <si>
+    <t>{{client.city}}</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
+  </si>
+  <si>
+    <t>Linked product's SKU (the Code column)</t>
+  </si>
+  <si>
+    <t>Line item description (Désignation)</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Tax Rate</t>
-  </si>
-  <si>
-    <t>Line Total</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
+    <t>Unit price, formatted with currency</t>
   </si>
   <si>
     <t>{{lineItems.taxRate}}</t>
   </si>
   <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Subtotal</t>
-  </si>
-  <si>
-    <t>{{invoice.subTotal}}</t>
-  </si>
-  <si>
-    <t>Tax</t>
-  </si>
-  <si>
-    <t>{{invoice.taxTotal}}</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>{{invoice.total}}</t>
-  </si>
-  <si>
-    <t>Payment terms: {{invoice.paymentTerms}}</t>
-  </si>
-  <si>
-    <t>IBAN: {{organization.iban}} | Bank: {{organization.bankName}}</t>
-  </si>
-  <si>
-    <t>Fiscal stamp: {{invoice.fiscalStampAmount}}</t>
+    <t>Tax rate percentage (e.g. 19.5%)</t>
+  </si>
+  <si>
+    <t>Quantity x unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>VAT recap</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per distinct tax rate</t>
+  </si>
+  <si>
+    <t>Tax rate percentage (e.g. 19%)</t>
+  </si>
+  <si>
+    <t>Taxable base for this rate, net of its share of the discount</t>
+  </si>
+  <si>
+    <t>VAT amount for this rate</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Total Brut HTVA — subtotal before discount and tax</t>
+  </si>
+  <si>
+    <t>Remise — flat pre-tax discount</t>
+  </si>
+  <si>
+    <t>Total Net HTVA — subtotal minus discount</t>
+  </si>
+  <si>
+    <t>Total TTC — grand total</t>
+  </si>
+  <si>
+    <t>{{invoice.paymentTerms}}</t>
+  </si>
+  <si>
+    <t>Payment terms text</t>
+  </si>
+  <si>
+    <t>Tunisia timbre fiscal — flat duty, formatted with currency (0 if unused)</t>
   </si>
   <si>
     <t>{{invoice.withholdingTaxLine}}</t>
   </si>
   <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>{{invoice.number}}</t>
-  </si>
-  <si>
-    <t>Invoice number</t>
-  </si>
-  <si>
-    <t>{{invoice.date}}</t>
-  </si>
-  <si>
-    <t>Invoice date</t>
-  </si>
-  <si>
-    <t>{{invoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Payment due date</t>
-  </si>
-  <si>
-    <t>{{invoice.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{invoice.buyerReference}}</t>
-  </si>
-  <si>
-    <t>Buyer reference (e.g. a Leitweg-ID)</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>Customer name</t>
-  </si>
-  <si>
-    <t>{{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Customer VAT number</t>
-  </si>
-  <si>
-    <t>{{client.email}}</t>
-  </si>
-  <si>
-    <t>Customer email</t>
-  </si>
-  <si>
-    <t>{{client.phone}}</t>
-  </si>
-  <si>
-    <t>Customer phone</t>
-  </si>
-  <si>
-    <t>{{client.street}}</t>
-  </si>
-  <si>
-    <t>Customer street</t>
-  </si>
-  <si>
-    <t>{{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Customer house number</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}}</t>
-  </si>
-  <si>
-    <t>Customer postal code</t>
-  </si>
-  <si>
-    <t>{{client.city}}</t>
-  </si>
-  <si>
-    <t>Customer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
-  </si>
-  <si>
-    <t>Linked product's SKU, blank on a free-text line or an unset SKU</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>Unit price, formatted with currency</t>
-  </si>
-  <si>
-    <t>Tax rate percentage (e.g. 19.5%)</t>
-  </si>
-  <si>
-    <t>Quantity x unit price, formatted with currency</t>
-  </si>
-  <si>
-    <t>Footer</t>
-  </si>
-  <si>
-    <t>Subtotal before tax</t>
-  </si>
-  <si>
-    <t>Total tax</t>
-  </si>
-  <si>
-    <t>Grand total</t>
-  </si>
-  <si>
-    <t>{{invoice.paymentTerms}}</t>
-  </si>
-  <si>
-    <t>Payment terms text</t>
-  </si>
-  <si>
-    <t>{{invoice.fiscalStampAmount}}</t>
-  </si>
-  <si>
-    <t>Tunisia timbre fiscal — flat duty, formatted with currency (0 if unused)</t>
-  </si>
-  <si>
-    <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (not just the rate/amount) if unset</t>
+    <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (if unset)</t>
+  </si>
+  <si>
+    <t>Whole "Arrêtée la présente facture à la somme de ..." sentence, blank unless enabled in Formatting settings</t>
   </si>
   <si>
     <t>{{organization.iban}}</t>
@@ -329,9 +410,6 @@
     <t>Seller IBAN</t>
   </si>
   <si>
-    <t>{{organization.bankName}}</t>
-  </si>
-  <si>
     <t>Seller bank name</t>
   </si>
   <si>
@@ -341,7 +419,7 @@
     <t>{{export.generatedDate}}</t>
   </si>
   <si>
-    <t>Date this file was exported (not the invoice's own date), in the organization's date format</t>
+    <t>Date this file was exported, in the organization's date format</t>
   </si>
   <si>
     <t>{{export.generatedTime}}</t>
@@ -353,14 +431,14 @@
     <t>&amp;P (page number) / &amp;N (total pages)</t>
   </si>
   <si>
-    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
+    <t>Native Excel/LibreOffice codes — only work in Page Layout ▸ Header/Footer, never a regular cell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -381,13 +459,19 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
       <color/>
       <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
@@ -404,16 +488,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -421,11 +505,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -433,22 +531,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -724,165 +834,231 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="22"/>
-    <col customWidth="true" max="2" min="2" width="40"/>
-    <col customWidth="true" max="5" min="3" width="14"/>
-    <col customWidth="true" max="6" min="6" width="16"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="34"/>
+    <col customWidth="true" max="5" min="3" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>10</v>
+      <c r="A7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="E12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="J12" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G14" t="s">
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="s">
         <v>27</v>
       </c>
+      <c r="B16" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="17">
-      <c r="E17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>29</v>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18">
-      <c r="E18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>31</v>
+      <c r="D18" t="s">
+        <v>37</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="19">
-      <c r="E19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>35</v>
+      <c r="D19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="D20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>37</v>
+      <c r="A24" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="D27:G27"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D31:G31"/>
+  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -901,373 +1077,475 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>38</v>
+      <c r="A1" s="9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>39</v>
+      <c r="A2" s="12" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>16</v>
+      <c r="A4" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>42</v>
+      <c r="A5" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="s">
-        <v>85</v>
+      <c r="B28" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>23</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="s">
-        <v>24</v>
-      </c>
-      <c r="C33" t="s">
-        <v>89</v>
+      <c r="A33" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C35" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="s">
-        <v>92</v>
+      <c r="B36" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C38" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="C40" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="s">
-        <v>98</v>
-      </c>
-      <c r="C41" t="s">
-        <v>99</v>
+      <c r="A41" s="11" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>103</v>
+        <v>28</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="s">
-        <v>105</v>
+      <c r="B45" t="s">
+        <v>29</v>
+      </c>
+      <c r="C45" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="s">
-        <v>106</v>
-      </c>
-      <c r="C46" t="s">
-        <v>107</v>
+      <c r="A46" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="C47" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
       <c r="C48" t="s">
-        <v>111</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="s">
+        <v>122</v>
+      </c>
+      <c r="C52" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="s">
+        <v>125</v>
+      </c>
+      <c r="C54" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="s">
+        <v>43</v>
+      </c>
+      <c r="C55" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="s">
+        <v>128</v>
+      </c>
+      <c r="C56" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="s">
+        <v>134</v>
+      </c>
+      <c r="C60" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="s">
+        <v>136</v>
+      </c>
+      <c r="C61" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A41:C41"/>
+    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A58:C58"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -7,11 +7,11 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Facture" sheetId="1" r:id="rId1"/>
+    <sheet name="Invoice" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Facture'!$1:$11</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Invoice'!$1:$13</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
@@ -20,394 +20,394 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
   <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>{{organization.email}} | {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>INVOICE</t>
+  </si>
+  <si>
+    <t>Invoice number: {{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Date: {{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Due date: {{invoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Buyer reference: {{invoice.buyerReference}}</t>
+  </si>
+  <si>
+    <t>Bill To</t>
+  </si>
+  <si>
+    <t>{{client.name}}</t>
+  </si>
+  <si>
+    <t>{{client.street}} {{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}} {{client.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Line Total</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitPrice}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.taxRate}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Subtotal</t>
+  </si>
+  <si>
+    <t>{{invoice.subTotal}}</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>{{invoice.discountAmount}}</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>{{invoice.taxTotal}}</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>{{invoice.total}}</t>
+  </si>
+  <si>
+    <t>Payment terms: {{invoice.paymentTerms}}</t>
+  </si>
+  <si>
+    <t>IBAN: {{organization.iban}} | Bank: {{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Fiscal stamp: {{invoice.fiscalStampAmount}}</t>
+  </si>
+  <si>
+    <t>{{invoice.withholdingTaxLine}}</t>
+  </si>
+  <si>
+    <t>{{invoice.amountInWords}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
     <t>{{organization.logo}}</t>
   </si>
   <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Tél : {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>MF : {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{client.name}}</t>
+    <t>Seller logo — place alone in a cell to anchor the uploaded image there (blank if the org has none)</t>
+  </si>
+  <si>
+    <t>{{invoice.number}}</t>
+  </si>
+  <si>
+    <t>Invoice number</t>
+  </si>
+  <si>
+    <t>{{invoice.date}}</t>
+  </si>
+  <si>
+    <t>Invoice date</t>
+  </si>
+  <si>
+    <t>{{invoice.dueDate}}</t>
+  </si>
+  <si>
+    <t>Payment due date</t>
+  </si>
+  <si>
+    <t>{{invoice.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{invoice.buyerReference}}</t>
+  </si>
+  <si>
+    <t>Buyer reference (e.g. a Leitweg-ID)</t>
+  </si>
+  <si>
+    <t>Seller company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Seller VAT / MF number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Seller email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Seller phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Seller website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Seller street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Seller house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Seller postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Seller city</t>
+  </si>
+  <si>
+    <t>Customer name</t>
+  </si>
+  <si>
+    <t>{{client.vatin}}</t>
+  </si>
+  <si>
+    <t>Customer VAT / MF number</t>
+  </si>
+  <si>
+    <t>{{client.identityNumber}}</t>
+  </si>
+  <si>
+    <t>Customer national ID / CIN number</t>
   </si>
   <si>
     <t>{{client.address}}</t>
   </si>
   <si>
-    <t>{{client.postalCode}} {{client.city}}</t>
-  </si>
-  <si>
-    <t>Tel: {{client.phone}}</t>
-  </si>
-  <si>
-    <t>CIN: {{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Facture N°: {{invoice.number}}</t>
-  </si>
-  <si>
-    <t>Date : {{invoice.date}}</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Désignation</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>P.U HT</t>
-  </si>
-  <si>
-    <t>TOTAL HT</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitPrice}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Taux TVA %</t>
-  </si>
-  <si>
-    <t>Base TVA</t>
-  </si>
-  <si>
-    <t>Montant TVA</t>
+    <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>{{client.email}}</t>
+  </si>
+  <si>
+    <t>Customer email</t>
+  </si>
+  <si>
+    <t>{{client.phone}}</t>
+  </si>
+  <si>
+    <t>Customer phone</t>
+  </si>
+  <si>
+    <t>{{client.phone2}}</t>
+  </si>
+  <si>
+    <t>Customer phone 2</t>
+  </si>
+  <si>
+    <t>{{client.phone3}}</t>
+  </si>
+  <si>
+    <t>Customer phone 3</t>
+  </si>
+  <si>
+    <t>{{client.street}}</t>
+  </si>
+  <si>
+    <t>Customer street</t>
+  </si>
+  <si>
+    <t>{{client.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Customer house number</t>
+  </si>
+  <si>
+    <t>{{client.postalCode}}</t>
+  </si>
+  <si>
+    <t>Customer postal code</t>
+  </si>
+  <si>
+    <t>{{client.city}}</t>
+  </si>
+  <si>
+    <t>Customer city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
+  </si>
+  <si>
+    <t>Linked product's SKU (the Code column)</t>
+  </si>
+  <si>
+    <t>Line item description (Désignation)</t>
+  </si>
+  <si>
+    <t>Unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>Tax rate percentage (e.g. 19.5%)</t>
+  </si>
+  <si>
+    <t>Quantity x unit price, formatted with currency</t>
+  </si>
+  <si>
+    <t>VAT recap</t>
+  </si>
+  <si>
+    <t>{{#taxLines}}</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per distinct tax rate</t>
   </si>
   <si>
     <t>{{taxLines.rate}}</t>
   </si>
   <si>
+    <t>Tax rate percentage (e.g. 19%)</t>
+  </si>
+  <si>
     <t>{{taxLines.base}}</t>
   </si>
   <si>
+    <t>Taxable base for this rate, net of its share of the discount</t>
+  </si>
+  <si>
     <t>{{taxLines.amount}}</t>
   </si>
   <si>
-    <t>{{#taxLines}}</t>
-  </si>
-  <si>
-    <t>Total Brut HTVA</t>
-  </si>
-  <si>
-    <t>{{invoice.subTotal}}</t>
-  </si>
-  <si>
-    <t>Remise</t>
-  </si>
-  <si>
-    <t>{{invoice.discountAmount}}</t>
-  </si>
-  <si>
-    <t>Total Net HTVA</t>
+    <t>VAT amount for this rate</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Total Brut HTVA — subtotal before discount and tax</t>
+  </si>
+  <si>
+    <t>Remise — flat pre-tax discount</t>
   </si>
   <si>
     <t>{{invoice.netTaxable}}</t>
   </si>
   <si>
+    <t>Total Net HTVA — subtotal minus discount</t>
+  </si>
+  <si>
     <t>Total TVA</t>
   </si>
   <si>
-    <t>{{invoice.taxTotal}}</t>
-  </si>
-  <si>
-    <t>D.Timbre</t>
+    <t>Total TTC — grand total</t>
+  </si>
+  <si>
+    <t>{{invoice.paymentTerms}}</t>
+  </si>
+  <si>
+    <t>Payment terms text</t>
   </si>
   <si>
     <t>{{invoice.fiscalStampAmount}}</t>
   </si>
   <si>
-    <t>Total TTC</t>
-  </si>
-  <si>
-    <t>{{invoice.total}}</t>
-  </si>
-  <si>
-    <t>{{invoice.amountInWords}}</t>
-  </si>
-  <si>
-    <t>Cachet et Signature</t>
-  </si>
-  <si>
-    <t>IBAN : {{organization.iban}}</t>
+    <t>Tunisia timbre fiscal — flat duty, formatted with currency (0 if unused)</t>
+  </si>
+  <si>
+    <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (if unset)</t>
+  </si>
+  <si>
+    <t>Whole "Arrêtée la présente facture à la somme de ..." sentence, blank unless enabled in Formatting settings</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Seller IBAN</t>
   </si>
   <si>
     <t>{{organization.bankName}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Seller logo — place alone in a cell to anchor the uploaded image there (blank if the org has none)</t>
-  </si>
-  <si>
-    <t>{{invoice.number}}</t>
-  </si>
-  <si>
-    <t>Invoice number</t>
-  </si>
-  <si>
-    <t>{{invoice.date}}</t>
-  </si>
-  <si>
-    <t>Invoice date</t>
-  </si>
-  <si>
-    <t>{{invoice.dueDate}}</t>
-  </si>
-  <si>
-    <t>Payment due date</t>
-  </si>
-  <si>
-    <t>{{invoice.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{invoice.buyerReference}}</t>
-  </si>
-  <si>
-    <t>Buyer reference (e.g. a Leitweg-ID)</t>
-  </si>
-  <si>
-    <t>Seller company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Seller VAT / MF number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Seller email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Seller phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Seller website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Seller street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Seller house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Seller postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Seller city</t>
-  </si>
-  <si>
-    <t>Customer name</t>
-  </si>
-  <si>
-    <t>{{client.vatin}}</t>
-  </si>
-  <si>
-    <t>Customer VAT / MF number</t>
-  </si>
-  <si>
-    <t>{{client.identityNumber}}</t>
-  </si>
-  <si>
-    <t>Customer national ID / CIN number</t>
-  </si>
-  <si>
-    <t>Customer single-line address</t>
-  </si>
-  <si>
-    <t>{{client.email}}</t>
-  </si>
-  <si>
-    <t>Customer email</t>
-  </si>
-  <si>
-    <t>{{client.phone}}</t>
-  </si>
-  <si>
-    <t>Customer phone</t>
-  </si>
-  <si>
-    <t>{{client.phone2}}</t>
-  </si>
-  <si>
-    <t>Customer phone 2</t>
-  </si>
-  <si>
-    <t>{{client.phone3}}</t>
-  </si>
-  <si>
-    <t>Customer phone 3</t>
-  </si>
-  <si>
-    <t>{{client.street}}</t>
-  </si>
-  <si>
-    <t>Customer street</t>
-  </si>
-  <si>
-    <t>{{client.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Customer house number</t>
-  </si>
-  <si>
-    <t>{{client.postalCode}}</t>
-  </si>
-  <si>
-    <t>Customer postal code</t>
-  </si>
-  <si>
-    <t>{{client.city}}</t>
-  </si>
-  <si>
-    <t>Customer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
-  </si>
-  <si>
-    <t>Linked product's SKU (the Code column)</t>
-  </si>
-  <si>
-    <t>Line item description (Désignation)</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Unit price, formatted with currency</t>
-  </si>
-  <si>
-    <t>{{lineItems.taxRate}}</t>
-  </si>
-  <si>
-    <t>Tax rate percentage (e.g. 19.5%)</t>
-  </si>
-  <si>
-    <t>Quantity x unit price, formatted with currency</t>
-  </si>
-  <si>
-    <t>VAT recap</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per distinct tax rate</t>
-  </si>
-  <si>
-    <t>Tax rate percentage (e.g. 19%)</t>
-  </si>
-  <si>
-    <t>Taxable base for this rate, net of its share of the discount</t>
-  </si>
-  <si>
-    <t>VAT amount for this rate</t>
-  </si>
-  <si>
-    <t>Footer</t>
-  </si>
-  <si>
-    <t>Total Brut HTVA — subtotal before discount and tax</t>
-  </si>
-  <si>
-    <t>Remise — flat pre-tax discount</t>
-  </si>
-  <si>
-    <t>Total Net HTVA — subtotal minus discount</t>
-  </si>
-  <si>
-    <t>Total TTC — grand total</t>
-  </si>
-  <si>
-    <t>{{invoice.paymentTerms}}</t>
-  </si>
-  <si>
-    <t>Payment terms text</t>
-  </si>
-  <si>
-    <t>Tunisia timbre fiscal — flat duty, formatted with currency (0 if unused)</t>
-  </si>
-  <si>
-    <t>{{invoice.withholdingTaxLine}}</t>
-  </si>
-  <si>
-    <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (if unset)</t>
-  </si>
-  <si>
-    <t>Whole "Arrêtée la présente facture à la somme de ..." sentence, blank unless enabled in Formatting settings</t>
-  </si>
-  <si>
-    <t>{{organization.iban}}</t>
-  </si>
-  <si>
-    <t>Seller IBAN</t>
   </si>
   <si>
     <t>Seller bank name</t>
@@ -465,13 +465,13 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="14"/>
     </font>
     <font>
       <family val="2"/>
@@ -523,7 +523,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -549,10 +549,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -834,231 +837,178 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="34"/>
-    <col customWidth="true" max="5" min="3" width="16"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="5" min="3" width="14"/>
+    <col customWidth="true" max="6" min="6" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
+      <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="C13" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="F13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="5" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="J12" t="s">
+      <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D15" t="s">
+      <c r="G14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="5" t="s">
+    </row>
+    <row r="19">
+      <c r="E19" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F19" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="5" t="s">
+    </row>
+    <row r="20">
+      <c r="E20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="D17" t="s">
+      <c r="F20" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="5" t="s">
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18">
-      <c r="D18" t="s">
+    <row r="24">
+      <c r="A24" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="5" t="s">
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19">
-      <c r="D19" t="s">
+    <row r="26">
+      <c r="A26" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="5" t="s">
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20">
-      <c r="D20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="D27" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" t="s">
-        <v>46</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="D27:G27"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D31:G31"/>
-  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -1077,401 +1027,401 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>47</v>
+      <c r="A1" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>48</v>
+      <c r="A2" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>51</v>
+      <c r="A4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>52</v>
+      <c r="A5" s="12" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C32" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="s">
-        <v>103</v>
+      <c r="A33" s="12" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C37" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C40" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="s">
-        <v>112</v>
+      <c r="A41" s="12" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="s">
-        <v>117</v>
+      <c r="A46" s="12" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" t="s">
         <v>122</v>
-      </c>
-      <c r="C52" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="s">
-        <v>40</v>
+        <v>123</v>
       </c>
       <c r="C53" t="s">
         <v>124</v>
@@ -1479,38 +1429,38 @@
     </row>
     <row r="54">
       <c r="B54" t="s">
+        <v>39</v>
+      </c>
+      <c r="C54" t="s">
         <v>125</v>
-      </c>
-      <c r="C54" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" t="s">
         <v>128</v>
-      </c>
-      <c r="C56" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="s">
-        <v>46</v>
+        <v>129</v>
       </c>
       <c r="C57" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>131</v>
       </c>
     </row>

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -398,7 +398,7 @@
     <t>Full "Withholding tax (12%): 40.00 EUR" line, entirely blank (if unset)</t>
   </si>
   <si>
-    <t>Whole "Arrêtée la présente facture à la somme de ..." sentence, blank unless enabled in Formatting settings</t>
+    <t>Whole amount-in-words sentence in the organization's document language (French: "Arrêtée la présente facture à la somme de ..."), blank unless enabled in Formatting settings</t>
   </si>
   <si>
     <t>{{organization.iban}}</t>

--- a/db/templates/invoice_default.xlsx
+++ b/db/templates/invoice_default.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>{{organization.name}}</t>
   </si>
@@ -56,7 +56,7 @@
     <t>{{client.name}}</t>
   </si>
   <si>
-    <t>{{client.street}} {{client.houseNumber}}</t>
+    <t>{{client.addressLine}}</t>
   </si>
   <si>
     <t>{{client.postalCode}} {{client.city}}</t>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>Customer single-line address</t>
+  </si>
+  <si>
+    <t>Customer street and house number, or the single-line address when there is no street</t>
   </si>
   <si>
     <t>{{client.email}}</t>
@@ -1206,84 +1209,84 @@
     </row>
     <row r="25">
       <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" t="s">
         <v>82</v>
-      </c>
-      <c r="C25" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
         <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
         <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" t="s">
         <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" t="s">
         <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
         <v>92</v>
-      </c>
-      <c r="C30" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C31" t="s">
         <v>94</v>
-      </c>
-      <c r="C31" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="s">
+        <v>95</v>
+      </c>
+      <c r="C32" t="s">
         <v>96</v>
       </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="33">
+      <c r="B33" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="s">
+      <c r="C33" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="s">
-        <v>27</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="A34" s="12" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
         <v>100</v>
@@ -1291,7 +1294,7 @@
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
         <v>101</v>
@@ -1299,23 +1302,23 @@
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C37" t="s">
-        <v>17</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
-        <v>102</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C39" t="s">
         <v>103</v>
@@ -1323,65 +1326,65 @@
     </row>
     <row r="40">
       <c r="B40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C40" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="s">
+      <c r="B41" t="s">
+        <v>26</v>
+      </c>
+      <c r="C41" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="s">
+      <c r="A42" s="12" t="s">
         <v>106</v>
-      </c>
-      <c r="C42" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" t="s">
         <v>108</v>
-      </c>
-      <c r="C43" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
+        <v>109</v>
+      </c>
+      <c r="C44" t="s">
         <v>110</v>
-      </c>
-      <c r="C44" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" t="s">
         <v>112</v>
       </c>
-      <c r="C45" t="s">
+    </row>
+    <row r="46">
+      <c r="B46" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="s">
+      <c r="C46" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="A47" s="12" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C48" t="s">
         <v>116</v>
@@ -1389,15 +1392,15 @@
     </row>
     <row r="49">
       <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
         <v>117</v>
-      </c>
-      <c r="C49" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="C50" t="s">
         <v>119</v>
@@ -1405,7 +1408,7 @@
     </row>
     <row r="51">
       <c r="B51" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C51" t="s">
         <v>120</v>
@@ -1413,23 +1416,23 @@
     </row>
     <row r="52">
       <c r="B52" t="s">
+        <v>35</v>
+      </c>
+      <c r="C52" t="s">
         <v>121</v>
-      </c>
-      <c r="C52" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" t="s">
         <v>123</v>
-      </c>
-      <c r="C53" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
       <c r="C54" t="s">
         <v>125</v>
@@ -1437,7 +1440,7 @@
     </row>
     <row r="55">
       <c r="B55" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C55" t="s">
         <v>126</v>
@@ -1445,57 +1448,65 @@
     </row>
     <row r="56">
       <c r="B56" t="s">
+        <v>40</v>
+      </c>
+      <c r="C56" t="s">
         <v>127</v>
-      </c>
-      <c r="C56" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" t="s">
         <v>129</v>
       </c>
-      <c r="C57" t="s">
+    </row>
+    <row r="58">
+      <c r="B58" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="s">
+      <c r="C58" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="s">
+      <c r="A59" s="12" t="s">
         <v>132</v>
-      </c>
-      <c r="C59" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" t="s">
+        <v>133</v>
+      </c>
+      <c r="C60" t="s">
         <v>134</v>
-      </c>
-      <c r="C60" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" t="s">
+        <v>135</v>
+      </c>
+      <c r="C61" t="s">
         <v>136</v>
       </c>
-      <c r="C61" t="s">
+    </row>
+    <row r="62">
+      <c r="B62" t="s">
         <v>137</v>
+      </c>
+      <c r="C62" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A58:C58"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A59:C59"/>
   </mergeCells>
 </worksheet>
 </file>